--- a/artfynd/A 48126-2022 artfynd.xlsx
+++ b/artfynd/A 48126-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 48126-2022 artfynd.xlsx
+++ b/artfynd/A 48126-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1027,6 +1027,116 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>128328933</v>
+      </c>
+      <c r="B5" t="n">
+        <v>109300</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Artrik vägkant, Gtl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>709007</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6402462</v>
+      </c>
+      <c r="S5" t="n">
+        <v>50</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Lokrume</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-07-18</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-07-18</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>östraallaArvid deJong</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Magnus Stenmark</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Via Magnus Stenmark</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 48126-2022 artfynd.xlsx
+++ b/artfynd/A 48126-2022 artfynd.xlsx
@@ -1032,7 +1032,7 @@
         <v>128328933</v>
       </c>
       <c r="B5" t="n">
-        <v>109300</v>
+        <v>109305</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 48126-2022 artfynd.xlsx
+++ b/artfynd/A 48126-2022 artfynd.xlsx
@@ -1032,7 +1032,7 @@
         <v>128328933</v>
       </c>
       <c r="B5" t="n">
-        <v>109305</v>
+        <v>109398</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 48126-2022 artfynd.xlsx
+++ b/artfynd/A 48126-2022 artfynd.xlsx
@@ -1032,7 +1032,7 @@
         <v>128328933</v>
       </c>
       <c r="B5" t="n">
-        <v>109398</v>
+        <v>109422</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 48126-2022 artfynd.xlsx
+++ b/artfynd/A 48126-2022 artfynd.xlsx
@@ -1032,7 +1032,7 @@
         <v>128328933</v>
       </c>
       <c r="B5" t="n">
-        <v>109422</v>
+        <v>109435</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 48126-2022 artfynd.xlsx
+++ b/artfynd/A 48126-2022 artfynd.xlsx
@@ -1032,7 +1032,7 @@
         <v>128328933</v>
       </c>
       <c r="B5" t="n">
-        <v>109435</v>
+        <v>109444</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 48126-2022 artfynd.xlsx
+++ b/artfynd/A 48126-2022 artfynd.xlsx
@@ -1032,7 +1032,7 @@
         <v>128328933</v>
       </c>
       <c r="B5" t="n">
-        <v>109444</v>
+        <v>109449</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 48126-2022 artfynd.xlsx
+++ b/artfynd/A 48126-2022 artfynd.xlsx
@@ -1032,7 +1032,7 @@
         <v>128328933</v>
       </c>
       <c r="B5" t="n">
-        <v>109449</v>
+        <v>109477</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 48126-2022 artfynd.xlsx
+++ b/artfynd/A 48126-2022 artfynd.xlsx
@@ -1032,7 +1032,7 @@
         <v>128328933</v>
       </c>
       <c r="B5" t="n">
-        <v>109477</v>
+        <v>109490</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 48126-2022 artfynd.xlsx
+++ b/artfynd/A 48126-2022 artfynd.xlsx
@@ -1032,7 +1032,7 @@
         <v>128328933</v>
       </c>
       <c r="B5" t="n">
-        <v>109490</v>
+        <v>109494</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 48126-2022 artfynd.xlsx
+++ b/artfynd/A 48126-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,54 +675,53 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>100928451</v>
+        <v>100928014</v>
       </c>
       <c r="B2" t="n">
-        <v>105045</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57247</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220079</v>
+        <v>100038</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lokrume Nyplings, Gtl</t>
+          <t>Lokrume Nyplings 1:19, Gtl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>709159.3074245715</v>
+        <v>709062</v>
       </c>
       <c r="R2" t="n">
-        <v>6402165.907923299</v>
+        <v>6402365</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -773,7 +772,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -795,16 +793,11 @@
         <v>100927938</v>
       </c>
       <c r="B3" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -840,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>709159.3074245715</v>
+        <v>709160</v>
       </c>
       <c r="R3" t="n">
-        <v>6402165.907923299</v>
+        <v>6402166</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -912,43 +905,42 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>100928169</v>
+        <v>100927989</v>
       </c>
       <c r="B4" t="n">
-        <v>105045</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58420</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220079</v>
+        <v>102992</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Näktergal</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Luscinia luscinia</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -956,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>709060.9999960059</v>
+        <v>709062</v>
       </c>
       <c r="R4" t="n">
-        <v>6402365.788819394</v>
+        <v>6402365</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -991,7 +983,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1001,7 +993,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1010,7 +1002,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1029,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128328933</v>
+        <v>100928169</v>
       </c>
       <c r="B5" t="n">
-        <v>109494</v>
+        <v>108116</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1040,41 +1031,41 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220299</v>
+        <v>220079</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Artrik vägkant, Gtl</t>
+          <t>Lokrume Nyplings 1:19, Gtl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>709007</v>
+        <v>709062</v>
       </c>
       <c r="R5" t="n">
-        <v>6402462</v>
+        <v>6402365</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1098,17 +1089,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2022-05-17</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>östraallaArvid deJong</t>
+          <t>2022-05-17</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1117,25 +1113,356 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
+          <t>Sebastian Bolander</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Sebastian Bolander</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>100928451</v>
+      </c>
+      <c r="B6" t="n">
+        <v>108116</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220079</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Jordtistel</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Cirsium acaule</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Lokrume Nyplings, Gtl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>709160</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6402166</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Lokrume</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2022-05-17</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2022-05-17</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Sebastian Bolander</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Sebastian Bolander</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>128328933</v>
+      </c>
+      <c r="B7" t="n">
+        <v>110078</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Artrik vägkant, Gtl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>709007</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6402462</v>
+      </c>
+      <c r="S7" t="n">
+        <v>50</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Lokrume</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-07-18</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-07-18</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>östraallaArvid deJong</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
           <t>Magnus Stenmark</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
+      <c r="AX7" t="inlineStr">
         <is>
           <t>Via Magnus Stenmark</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr">
+      <c r="AY7" t="inlineStr">
         <is>
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>100928537</v>
+      </c>
+      <c r="B8" t="n">
+        <v>102560</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>222133</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Jungfrulin</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Polygala vulgaris</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Lokrume Nyplings, Gtl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>709160</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6402166</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Lokrume</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2022-05-17</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2022-05-17</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Sebastian Bolander</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Sebastian Bolander</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 48126-2022 artfynd.xlsx
+++ b/artfynd/A 48126-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -787,6 +792,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100928014</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -902,6 +912,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100927938</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1017,6 +1032,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100927989</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1129,6 +1149,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100928169</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1241,6 +1266,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100928451</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1349,6 +1379,11 @@
       <c r="AY7" t="inlineStr">
         <is>
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128328933</t>
         </is>
       </c>
     </row>
@@ -1463,8 +1498,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100928537</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>